--- a/outputs/1786501092_part_list.xlsx
+++ b/outputs/1786501092_part_list.xlsx
@@ -532,7 +532,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>BLXWFA000W2U</t>
+          <t>BS0100008V40</t>
         </is>
       </c>
     </row>
@@ -544,7 +544,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>BL0000001517</t>
+          <t>BSXR2A002527</t>
         </is>
       </c>
     </row>
@@ -556,7 +556,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>BLXWFA000W5H</t>
+          <t>BSXR2A003523</t>
         </is>
       </c>
     </row>
@@ -568,7 +568,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>BLXWFA0014QL</t>
+          <t>BSXR2A002141</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>BLXWHF02CF7C</t>
+          <t>BSXR2A002183</t>
         </is>
       </c>
     </row>
@@ -592,7 +592,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>BLXWHF02CF7D</t>
+          <t>BSXUFAE000E5</t>
         </is>
       </c>
     </row>
@@ -604,7 +604,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>BLXWHF02CF7A</t>
+          <t>BSXUFAF000E5</t>
         </is>
       </c>
     </row>
@@ -616,7 +616,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>BLXWHF029G3V</t>
+          <t>BSXUFAG001JC</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>BLXWFA00114N</t>
+          <t>BSXUFAH001RR</t>
         </is>
       </c>
     </row>
@@ -640,7 +640,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>BLXWFA00195F</t>
+          <t>BSXE00CBM023</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>BLXWFA000XJ0</t>
+          <t>BSXE00CC1006</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>BLXWFA0017SX</t>
+          <t>BSWU01007334</t>
         </is>
       </c>
     </row>
@@ -676,7 +676,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>BLXWFA001ABD</t>
+          <t>BSWU01007273</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>BLXWFA000V4X</t>
+          <t>BSWU01007150</t>
         </is>
       </c>
     </row>
@@ -700,7 +700,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>BLXWFA000W3D</t>
+          <t>BSWU01007408</t>
         </is>
       </c>
     </row>
@@ -712,7 +712,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>BLXWFA0014Q5</t>
+          <t>BSWU01007067</t>
         </is>
       </c>
     </row>
@@ -724,7 +724,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>BLXWFA000G6S</t>
+          <t>BSWU01007089</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>BLXWFA000GWM</t>
+          <t>BSXBG6537048</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>BS0100008V40</t>
+          <t>BSXWFA0009BF</t>
         </is>
       </c>
     </row>
@@ -760,7 +760,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>BLXWHF02CBFV</t>
+          <t>BSXWFA00094U</t>
         </is>
       </c>
     </row>
@@ -772,7 +772,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>BLXWHF029ANG</t>
+          <t>BLXWFA000W2U</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>BLXWHF02CBA6</t>
+          <t>BL0000001517</t>
         </is>
       </c>
     </row>
@@ -796,7 +796,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>BLXWHF029APK</t>
+          <t>BLXWFA000W5H</t>
         </is>
       </c>
     </row>
@@ -808,7 +808,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>BSXR2A002527</t>
+          <t>BLXWFA0014QL</t>
         </is>
       </c>
     </row>
@@ -820,7 +820,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>BSXR2A003523</t>
+          <t>BLXWHF02CF7C</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>BSXR2A002141</t>
+          <t>BLXWHF02CF7D</t>
         </is>
       </c>
     </row>
@@ -844,7 +844,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>BSXR2A002183</t>
+          <t>BLXWHF02CF7A</t>
         </is>
       </c>
     </row>
@@ -856,7 +856,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>BSXUFAE000E5</t>
+          <t>BLXWHF029G3V</t>
         </is>
       </c>
     </row>
@@ -868,7 +868,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>BSXUFAF000E5</t>
+          <t>BLXWFA00114N</t>
         </is>
       </c>
     </row>
@@ -880,7 +880,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>BL01000002X7</t>
+          <t>BLXWFA00195F</t>
         </is>
       </c>
     </row>
@@ -892,7 +892,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>BSXUFAG001JC</t>
+          <t>BLXWFA000XJ0</t>
         </is>
       </c>
     </row>
@@ -904,7 +904,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>BSXUFAH001RR</t>
+          <t>BLXWFA0017SX</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>BSXE00CBM023</t>
+          <t>BLXWFA001ABD</t>
         </is>
       </c>
     </row>
@@ -928,7 +928,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>BSXE00CC1006</t>
+          <t>BLXWFA000V4X</t>
         </is>
       </c>
     </row>
@@ -940,7 +940,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>BLXWFA000VET</t>
+          <t>BLXWFA000W3D</t>
         </is>
       </c>
     </row>
@@ -952,7 +952,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>BSWU01007334</t>
+          <t>BLXWFA0014Q5</t>
         </is>
       </c>
     </row>
@@ -964,7 +964,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>BSWU01007273</t>
+          <t>BLXWFA000G6S</t>
         </is>
       </c>
     </row>
@@ -976,7 +976,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>BSWU01007150</t>
+          <t>BLXWFA000GWM</t>
         </is>
       </c>
     </row>
@@ -988,7 +988,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>BSWU01007408</t>
+          <t>BLXWHF02CBFV</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>BSWU01007067</t>
+          <t>BLXWHF029ANG</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>BSWU01007089</t>
+          <t>BLXWHF02CBA6</t>
         </is>
       </c>
     </row>
@@ -1024,7 +1024,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>BSXBG6537048</t>
+          <t>BLXWHF029APK</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>BL01000001WQ</t>
+          <t>BL01000002X7</t>
         </is>
       </c>
     </row>
@@ -1048,7 +1048,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>BL01000001X5</t>
+          <t>BLXWFA000VET</t>
         </is>
       </c>
     </row>
@@ -1060,7 +1060,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>BSXWFA0009BF</t>
+          <t>BL01000001WQ</t>
         </is>
       </c>
     </row>
@@ -1072,7 +1072,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>BSXWFA00094U</t>
+          <t>BL01000001X5</t>
         </is>
       </c>
     </row>
